--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/6155-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/6155-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6AE57201-06BB-4CE3-A169-69E123A0E609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A50DE6FC-614B-4D0E-BAAC-69D410B3EDD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{7AD8919F-8C7A-4F1D-B0F8-21A1238B836D}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{2C70B032-0E92-4DF1-8A93-3AB81B2C4F9A}"/>
   </bookViews>
   <sheets>
     <sheet name="6155-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1571,29 +1571,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DB1BBB0-FA5F-4F62-8B67-AEA83C5C6B97}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{739D6E5C-9F7E-45FD-83F0-E53075156C65}">
   <dimension ref="A1:X38"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1627,7 +1626,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1663,7 +1662,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1715,7 +1714,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1783,7 +1782,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1855,7 +1854,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39">
         <v>2023</v>
       </c>
@@ -1927,7 +1926,7 @@
         <v>3.57</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2022</v>
       </c>
@@ -1999,7 +1998,7 @@
         <v>6.56</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="39">
         <v>2021</v>
       </c>
@@ -2071,7 +2070,7 @@
         <v>4.2699999999999996</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2020</v>
       </c>
@@ -2143,7 +2142,7 @@
         <v>3.54</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="39">
         <v>2019</v>
       </c>
@@ -2215,7 +2214,7 @@
         <v>6.71</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="37">
         <v>2018</v>
       </c>
@@ -2287,7 +2286,7 @@
         <v>5.26</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="39">
         <v>2017</v>
       </c>
@@ -2359,7 +2358,7 @@
         <v>2.4900000000000002</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2016</v>
       </c>
@@ -2431,7 +2430,7 @@
         <v>4.93</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="39">
         <v>2015</v>
       </c>
@@ -2503,7 +2502,7 @@
         <v>7.42</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="37">
         <v>2014</v>
       </c>
@@ -2575,7 +2574,7 @@
         <v>9.2200000000000006</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="41">
         <v>2013</v>
       </c>
@@ -2647,7 +2646,7 @@
         <v>9.09</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="43"/>
       <c r="B17" s="44"/>
       <c r="C17" s="18" t="s">
@@ -2675,7 +2674,7 @@
       <c r="W17" s="50"/>
       <c r="X17" s="46"/>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="37">
         <v>2012</v>
       </c>
@@ -2747,7 +2746,7 @@
         <v>7.12</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="39">
         <v>2011</v>
       </c>
@@ -2819,7 +2818,7 @@
         <v>7.09</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="37">
         <v>2010</v>
       </c>
@@ -2891,7 +2890,7 @@
         <v>7.56</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="41">
         <v>2009</v>
       </c>
@@ -2963,7 +2962,7 @@
         <v>8.36</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="43"/>
       <c r="B22" s="44"/>
       <c r="C22" s="18" t="s">
@@ -2991,7 +2990,7 @@
       <c r="W22" s="50"/>
       <c r="X22" s="46"/>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="51">
         <v>2008</v>
       </c>
@@ -3063,7 +3062,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="53"/>
       <c r="B24" s="54"/>
       <c r="C24" s="20" t="s">
@@ -3091,7 +3090,7 @@
       <c r="W24" s="60"/>
       <c r="X24" s="56"/>
     </row>
-    <row r="25" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="41">
         <v>2007</v>
       </c>
@@ -3163,7 +3162,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="43"/>
       <c r="B26" s="44"/>
       <c r="C26" s="18" t="s">
@@ -3191,7 +3190,7 @@
       <c r="W26" s="50"/>
       <c r="X26" s="46"/>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="51">
         <v>2006</v>
       </c>
@@ -3263,7 +3262,7 @@
         <v>8.82</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="53"/>
       <c r="B28" s="54"/>
       <c r="C28" s="20" t="s">
@@ -3291,7 +3290,7 @@
       <c r="W28" s="60"/>
       <c r="X28" s="56"/>
     </row>
-    <row r="29" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="39">
         <v>2005</v>
       </c>
@@ -3363,7 +3362,7 @@
         <v>8.1199999999999992</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="37">
         <v>2004</v>
       </c>
@@ -3435,7 +3434,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="39">
         <v>2003</v>
       </c>
@@ -3507,7 +3506,7 @@
         <v>8.0299999999999994</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="51">
         <v>2002</v>
       </c>
@@ -3579,7 +3578,7 @@
         <v>7.14</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="53"/>
       <c r="B33" s="54"/>
       <c r="C33" s="20" t="s">
@@ -3607,7 +3606,7 @@
       <c r="W33" s="60"/>
       <c r="X33" s="56"/>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="39">
         <v>2001</v>
       </c>
@@ -3679,7 +3678,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="37">
         <v>2000</v>
       </c>
@@ -3751,7 +3750,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="39">
         <v>1999</v>
       </c>
@@ -3823,7 +3822,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="37">
         <v>1998</v>
       </c>
@@ -3895,7 +3894,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="39" t="s">
         <v>59</v>
       </c>
